--- a/feature/evolutionRDVV3/ig/StructureDefinition-FrPractitionerRegul.xlsx
+++ b/feature/evolutionRDVV3/ig/StructureDefinition-FrPractitionerRegul.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:22:08+00:00</t>
+    <t>2026-09-09T15:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/evolutionRDVV3/ig/StructureDefinition-FrPractitionerRegul.xlsx
+++ b/feature/evolutionRDVV3/ig/StructureDefinition-FrPractitionerRegul.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:39:29+00:00</t>
+    <t>2026-09-10T09:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/evolutionRDVV3/ig/StructureDefinition-FrPractitionerRegul.xlsx
+++ b/feature/evolutionRDVV3/ig/StructureDefinition-FrPractitionerRegul.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:13:18+00:00</t>
+    <t>2026-09-11T09:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/evolutionRDVV3/ig/StructureDefinition-FrPractitionerRegul.xlsx
+++ b/feature/evolutionRDVV3/ig/StructureDefinition-FrPractitionerRegul.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T09:05:46+00:00</t>
+    <t>2026-09-11T09:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
